--- a/job_application_forms/020_locksmith_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/020_locksmith_job_application_form--job_application_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>confirm_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Confirm 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>review_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>confirm_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Confirm 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>confirm_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Confirm 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
